--- a/output/CustExp Configuration.xlsx
+++ b/output/CustExp Configuration.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRS102" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRS125" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRS117" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OIS010" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -254,8 +255,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -973,9 +974,19 @@
       <c r="Z9" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="11" t="n"/>
+      <c r="A10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Customer Order Types</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>OIS010</t>
+        </is>
+      </c>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="1" t="n"/>
       <c r="F10" s="1" t="n"/>
@@ -1003,7 +1014,7 @@
     <row r="11">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="6" t="n"/>
-      <c r="C11" s="12" t="n"/>
+      <c r="C11" s="11" t="n"/>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="1" t="n"/>
       <c r="F11" s="1" t="n"/>
@@ -1031,7 +1042,7 @@
     <row r="12">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="6" t="n"/>
-      <c r="C12" s="11" t="n"/>
+      <c r="C12" s="12" t="n"/>
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="1" t="n"/>
       <c r="F12" s="1" t="n"/>
@@ -28730,6 +28741,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56823,25 +56835,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.2" customWidth="1" min="1" max="1"/>
-    <col width="13.2" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15.6" customWidth="1" min="4" max="4"/>
-    <col width="7.199999999999999" customWidth="1" min="5" max="5"/>
-    <col width="14.4" customWidth="1" min="6" max="6"/>
-    <col width="14.4" customWidth="1" min="7" max="7"/>
-    <col width="10.8" customWidth="1" min="8" max="8"/>
-    <col width="34.8" customWidth="1" min="9" max="9"/>
-    <col width="34.8" customWidth="1" min="10" max="10"/>
-    <col width="33.6" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19.2" customWidth="1" min="2" max="2"/>
+    <col width="13.2" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15.6" customWidth="1" min="5" max="5"/>
+    <col width="7.199999999999999" customWidth="1" min="6" max="6"/>
+    <col width="26.4" customWidth="1" min="7" max="7"/>
+    <col width="26.4" customWidth="1" min="8" max="8"/>
+    <col width="26.4" customWidth="1" min="9" max="9"/>
+    <col width="26.4" customWidth="1" min="10" max="10"/>
+    <col width="26.4" customWidth="1" min="11" max="11"/>
     <col width="26.4" customWidth="1" min="12" max="12"/>
-    <col width="43.2" customWidth="1" min="13" max="13"/>
-    <col width="13.2" customWidth="1" min="14" max="14"/>
+    <col width="26.4" customWidth="1" min="13" max="13"/>
+    <col width="26.4" customWidth="1" min="14" max="14"/>
     <col width="26.4" customWidth="1" min="15" max="15"/>
-    <col width="33.6" customWidth="1" min="16" max="16"/>
+    <col width="26.4" customWidth="1" min="16" max="16"/>
+    <col width="26.4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -56868,162 +56881,172 @@
     <row r="5">
       <c r="A5" s="27" t="inlineStr">
         <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
           <t>Constant value</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Key value</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Language</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
-        <is>
-          <t>Terms text</t>
-        </is>
-      </c>
       <c r="G5" s="27" t="inlineStr">
         <is>
-          <t>Terms text</t>
+          <t>Reference field TEL1</t>
         </is>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Reference field TEL2</t>
         </is>
       </c>
       <c r="I5" s="27" t="inlineStr">
         <is>
-          <t>Adjustment factor consignee</t>
+          <t>Reference field RCPY</t>
         </is>
       </c>
       <c r="J5" s="27" t="inlineStr">
         <is>
-          <t>Adjustment factor consignor</t>
+          <t>Reference field ADJR</t>
         </is>
       </c>
       <c r="K5" s="27" t="inlineStr">
         <is>
-          <t>Delivery terms - INTRASTAT</t>
+          <t>Reference field ADJS</t>
         </is>
       </c>
       <c r="L5" s="27" t="inlineStr">
         <is>
-          <t>Goods responsibility</t>
+          <t>Reference field ECDT</t>
         </is>
       </c>
       <c r="M5" s="27" t="inlineStr">
         <is>
-          <t>Delivery terms - Extrastat (Extra)</t>
+          <t>Reference field DELT</t>
         </is>
       </c>
       <c r="N5" s="27" t="inlineStr">
         <is>
-          <t>Tax point</t>
+          <t>Reference field EXTD</t>
         </is>
       </c>
       <c r="O5" s="27" t="inlineStr">
         <is>
-          <t>Freight cost control</t>
+          <t>Reference field TXPO</t>
         </is>
       </c>
       <c r="P5" s="27" t="inlineStr">
         <is>
-          <t>Fiscal representative rule</t>
+          <t>Reference field FRCK</t>
+        </is>
+      </c>
+      <c r="Q5" s="27" t="inlineStr">
+        <is>
+          <t>Reference field FRRU</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="28" t="inlineStr">
         <is>
+          <t>DIVI</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
           <t>STCO</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>STKY</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>LNCD</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>TX40</t>
         </is>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>TX15</t>
         </is>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>TEL1</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="H6" s="28" t="inlineStr">
         <is>
           <t>TEL2</t>
         </is>
       </c>
-      <c r="H6" s="28" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t>RCPY</t>
         </is>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="J6" s="28" t="inlineStr">
         <is>
           <t>ADJR</t>
         </is>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="K6" s="28" t="inlineStr">
         <is>
           <t>ADJS</t>
         </is>
       </c>
-      <c r="K6" s="28" t="inlineStr">
+      <c r="L6" s="28" t="inlineStr">
         <is>
           <t>ECDT</t>
         </is>
       </c>
-      <c r="L6" s="28" t="inlineStr">
+      <c r="M6" s="28" t="inlineStr">
         <is>
           <t>DELT</t>
         </is>
       </c>
-      <c r="M6" s="28" t="inlineStr">
+      <c r="N6" s="28" t="inlineStr">
         <is>
           <t>EXTD</t>
         </is>
       </c>
-      <c r="N6" s="28" t="inlineStr">
+      <c r="O6" s="28" t="inlineStr">
         <is>
           <t>TXPO</t>
         </is>
       </c>
-      <c r="O6" s="28" t="inlineStr">
+      <c r="P6" s="28" t="inlineStr">
         <is>
           <t>FRCK</t>
         </is>
       </c>
-      <c r="P6" s="28" t="inlineStr">
+      <c r="Q6" s="28" t="inlineStr">
         <is>
           <t>FRRU</t>
         </is>
@@ -57067,45 +57090,50 @@
       </c>
       <c r="H7" s="29" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I7" s="29" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="J7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J7" s="29" t="inlineStr">
+      <c r="K7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K7" s="29" t="inlineStr">
+      <c r="L7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L7" s="29" t="inlineStr">
+      <c r="M7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M7" s="29" t="inlineStr">
+      <c r="N7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="N7" s="29" t="inlineStr">
+      <c r="O7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O7" s="29" t="inlineStr">
+      <c r="P7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P7" s="29" t="inlineStr">
+      <c r="Q7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -57114,49 +57142,51 @@
     <row r="8">
       <c r="A8" s="30" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
-      </c>
-      <c r="F8" s="30" t="n">
-        <v>36</v>
       </c>
       <c r="G8" s="30" t="n">
         <v>36</v>
       </c>
       <c r="H8" s="30" t="n">
+        <v>36</v>
+      </c>
+      <c r="I8" s="30" t="n">
         <v>1</v>
-      </c>
-      <c r="I8" s="30" t="n">
-        <v>5</v>
       </c>
       <c r="J8" s="30" t="n">
         <v>5</v>
       </c>
       <c r="K8" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" s="30" t="n">
         <v>4</v>
-      </c>
-      <c r="L8" s="30" t="n">
-        <v>1</v>
       </c>
       <c r="M8" s="30" t="n">
         <v>1</v>
@@ -57168,6 +57198,9 @@
         <v>1</v>
       </c>
       <c r="P8" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -57185,18 +57218,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.2" customWidth="1" min="1" max="1"/>
-    <col width="13.2" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15.6" customWidth="1" min="4" max="4"/>
-    <col width="7.199999999999999" customWidth="1" min="5" max="5"/>
-    <col width="14.4" customWidth="1" min="6" max="6"/>
-    <col width="14.4" customWidth="1" min="7" max="7"/>
-    <col width="44.4" customWidth="1" min="8" max="8"/>
-    <col width="19.2" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19.2" customWidth="1" min="2" max="2"/>
+    <col width="13.2" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15.6" customWidth="1" min="5" max="5"/>
+    <col width="7.199999999999999" customWidth="1" min="6" max="6"/>
+    <col width="26.4" customWidth="1" min="7" max="7"/>
+    <col width="26.4" customWidth="1" min="8" max="8"/>
+    <col width="26.4" customWidth="1" min="9" max="9"/>
+    <col width="26.4" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -57223,92 +57257,102 @@
     <row r="5">
       <c r="A5" s="27" t="inlineStr">
         <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
           <t>Constant value</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Key value</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Language</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
-        <is>
-          <t>Terms text</t>
-        </is>
-      </c>
       <c r="G5" s="27" t="inlineStr">
         <is>
-          <t>Terms text</t>
+          <t>Reference field TEL1</t>
         </is>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>Transport method - trade stat (TST)</t>
+          <t>Reference field TEL2</t>
         </is>
       </c>
       <c r="I5" s="27" t="inlineStr">
         <is>
-          <t>Container used</t>
+          <t>Reference field VRDL</t>
+        </is>
+      </c>
+      <c r="J5" s="27" t="inlineStr">
+        <is>
+          <t>Reference field COTT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="28" t="inlineStr">
         <is>
+          <t>DIVI</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
           <t>STCO</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>STKY</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>LNCD</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>TX40</t>
         </is>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>TX15</t>
         </is>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>TEL1</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="H6" s="28" t="inlineStr">
         <is>
           <t>TEL2</t>
         </is>
       </c>
-      <c r="H6" s="28" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t>VRDL</t>
         </is>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="J6" s="28" t="inlineStr">
         <is>
           <t>COTT</t>
         </is>
@@ -57352,10 +57396,15 @@
       </c>
       <c r="H7" s="29" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I7" s="29" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="J7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -57364,39 +57413,44 @@
     <row r="8">
       <c r="A8" s="30" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
-      </c>
-      <c r="F8" s="30" t="n">
-        <v>36</v>
       </c>
       <c r="G8" s="30" t="n">
         <v>36</v>
       </c>
       <c r="H8" s="30" t="n">
+        <v>36</v>
+      </c>
+      <c r="I8" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="30" t="n">
+      <c r="J8" s="30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -57414,15 +57468,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.2" customWidth="1" min="1" max="1"/>
-    <col width="13.2" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15.6" customWidth="1" min="4" max="4"/>
-    <col width="7.199999999999999" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19.2" customWidth="1" min="2" max="2"/>
+    <col width="13.2" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15.6" customWidth="1" min="5" max="5"/>
+    <col width="7.199999999999999" customWidth="1" min="6" max="6"/>
+    <col width="26.4" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -57449,62 +57504,72 @@
     <row r="5">
       <c r="A5" s="27" t="inlineStr">
         <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
           <t>Constant value</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Key value</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Language</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
-        <is>
-          <t>Reference fld PARM</t>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>Reference field PARM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="28" t="inlineStr">
         <is>
+          <t>DIVI</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
           <t>STCO</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>STKY</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>LNCD</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>TX40</t>
         </is>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>TX15</t>
         </is>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>PARM</t>
         </is>
@@ -57541,34 +57606,44 @@
           <t>A</t>
         </is>
       </c>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="30" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="G8" s="30" t="n">
         <v>200</v>
       </c>
     </row>
@@ -57586,16 +57661,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.2" customWidth="1" min="1" max="1"/>
-    <col width="13.2" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15.6" customWidth="1" min="4" max="4"/>
-    <col width="7.199999999999999" customWidth="1" min="5" max="5"/>
-    <col width="14.4" customWidth="1" min="6" max="6"/>
-    <col width="14.4" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19.2" customWidth="1" min="2" max="2"/>
+    <col width="13.2" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15.6" customWidth="1" min="5" max="5"/>
+    <col width="7.199999999999999" customWidth="1" min="6" max="6"/>
+    <col width="26.4" customWidth="1" min="7" max="7"/>
+    <col width="26.4" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -57622,72 +57698,82 @@
     <row r="5">
       <c r="A5" s="27" t="inlineStr">
         <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
           <t>Constant value</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Key value</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Language</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
-        <is>
-          <t>Terms text</t>
-        </is>
-      </c>
       <c r="G5" s="27" t="inlineStr">
         <is>
-          <t>Terms text</t>
+          <t>Reference field TEL1</t>
+        </is>
+      </c>
+      <c r="H5" s="27" t="inlineStr">
+        <is>
+          <t>Reference field TEL2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="28" t="inlineStr">
         <is>
+          <t>DIVI</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
           <t>STCO</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>STKY</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>LNCD</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>TX40</t>
         </is>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>TX15</t>
         </is>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>TEL1</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="H6" s="28" t="inlineStr">
         <is>
           <t>TEL2</t>
         </is>
@@ -57729,37 +57815,47 @@
           <t>A</t>
         </is>
       </c>
+      <c r="H7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="30" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="G8" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="H8" s="30" t="n">
         <v>36</v>
       </c>
     </row>
@@ -57964,4 +58060,2887 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:EE8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25.2" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26.4" customWidth="1" min="3" max="3"/>
+    <col width="15.6" customWidth="1" min="4" max="4"/>
+    <col width="7.199999999999999" customWidth="1" min="5" max="5"/>
+    <col width="25.2" customWidth="1" min="6" max="6"/>
+    <col width="26.4" customWidth="1" min="7" max="7"/>
+    <col width="19.2" customWidth="1" min="8" max="8"/>
+    <col width="27.6" customWidth="1" min="9" max="9"/>
+    <col width="16.8" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="21.6" customWidth="1" min="13" max="13"/>
+    <col width="20.4" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="20.4" customWidth="1" min="16" max="16"/>
+    <col width="48" customWidth="1" min="17" max="17"/>
+    <col width="31.2" customWidth="1" min="18" max="18"/>
+    <col width="26.4" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="22.8" customWidth="1" min="21" max="21"/>
+    <col width="32.4" customWidth="1" min="22" max="22"/>
+    <col width="31.2" customWidth="1" min="23" max="23"/>
+    <col width="36" customWidth="1" min="24" max="24"/>
+    <col width="19.2" customWidth="1" min="25" max="25"/>
+    <col width="22.8" customWidth="1" min="26" max="26"/>
+    <col width="28.8" customWidth="1" min="27" max="27"/>
+    <col width="20.4" customWidth="1" min="28" max="28"/>
+    <col width="40.8" customWidth="1" min="29" max="29"/>
+    <col width="30" customWidth="1" min="30" max="30"/>
+    <col width="32.4" customWidth="1" min="31" max="31"/>
+    <col width="27.6" customWidth="1" min="32" max="32"/>
+    <col width="32.4" customWidth="1" min="33" max="33"/>
+    <col width="22.8" customWidth="1" min="34" max="34"/>
+    <col width="20.4" customWidth="1" min="35" max="35"/>
+    <col width="21.6" customWidth="1" min="36" max="36"/>
+    <col width="27.6" customWidth="1" min="37" max="37"/>
+    <col width="33.6" customWidth="1" min="38" max="38"/>
+    <col width="30" customWidth="1" min="39" max="39"/>
+    <col width="25.2" customWidth="1" min="40" max="40"/>
+    <col width="39.6" customWidth="1" min="41" max="41"/>
+    <col width="30" customWidth="1" min="42" max="42"/>
+    <col width="21.6" customWidth="1" min="43" max="43"/>
+    <col width="25.2" customWidth="1" min="44" max="44"/>
+    <col width="24" customWidth="1" min="45" max="45"/>
+    <col width="19.2" customWidth="1" min="46" max="46"/>
+    <col width="27.6" customWidth="1" min="47" max="47"/>
+    <col width="37.2" customWidth="1" min="48" max="48"/>
+    <col width="21.6" customWidth="1" min="49" max="49"/>
+    <col width="36" customWidth="1" min="50" max="50"/>
+    <col width="27.6" customWidth="1" min="51" max="51"/>
+    <col width="19.2" customWidth="1" min="52" max="52"/>
+    <col width="22.8" customWidth="1" min="53" max="53"/>
+    <col width="16.8" customWidth="1" min="54" max="54"/>
+    <col width="27.6" customWidth="1" min="55" max="55"/>
+    <col width="22.8" customWidth="1" min="56" max="56"/>
+    <col width="37.2" customWidth="1" min="57" max="57"/>
+    <col width="36" customWidth="1" min="58" max="58"/>
+    <col width="20.4" customWidth="1" min="59" max="59"/>
+    <col width="30" customWidth="1" min="60" max="60"/>
+    <col width="24" customWidth="1" min="61" max="61"/>
+    <col width="42" customWidth="1" min="62" max="62"/>
+    <col width="42" customWidth="1" min="63" max="63"/>
+    <col width="42" customWidth="1" min="64" max="64"/>
+    <col width="26.4" customWidth="1" min="65" max="65"/>
+    <col width="20.4" customWidth="1" min="66" max="66"/>
+    <col width="14.4" customWidth="1" min="67" max="67"/>
+    <col width="19.2" customWidth="1" min="68" max="68"/>
+    <col width="30" customWidth="1" min="69" max="69"/>
+    <col width="7.199999999999999" customWidth="1" min="70" max="70"/>
+    <col width="7.199999999999999" customWidth="1" min="71" max="71"/>
+    <col width="31.2" customWidth="1" min="72" max="72"/>
+    <col width="27.6" customWidth="1" min="73" max="73"/>
+    <col width="28.8" customWidth="1" min="74" max="74"/>
+    <col width="18" customWidth="1" min="75" max="75"/>
+    <col width="20.4" customWidth="1" min="76" max="76"/>
+    <col width="25.2" customWidth="1" min="77" max="77"/>
+    <col width="18" customWidth="1" min="78" max="78"/>
+    <col width="30" customWidth="1" min="79" max="79"/>
+    <col width="20.4" customWidth="1" min="80" max="80"/>
+    <col width="18" customWidth="1" min="81" max="81"/>
+    <col width="34.8" customWidth="1" min="82" max="82"/>
+    <col width="27.6" customWidth="1" min="83" max="83"/>
+    <col width="49.2" customWidth="1" min="84" max="84"/>
+    <col width="50" customWidth="1" min="85" max="85"/>
+    <col width="26.4" customWidth="1" min="86" max="86"/>
+    <col width="49.2" customWidth="1" min="87" max="87"/>
+    <col width="30" customWidth="1" min="88" max="88"/>
+    <col width="33.6" customWidth="1" min="89" max="89"/>
+    <col width="50" customWidth="1" min="90" max="90"/>
+    <col width="21.6" customWidth="1" min="91" max="91"/>
+    <col width="19.2" customWidth="1" min="92" max="92"/>
+    <col width="21.6" customWidth="1" min="93" max="93"/>
+    <col width="14.4" customWidth="1" min="94" max="94"/>
+    <col width="21.6" customWidth="1" min="95" max="95"/>
+    <col width="16.8" customWidth="1" min="96" max="96"/>
+    <col width="20.4" customWidth="1" min="97" max="97"/>
+    <col width="32.4" customWidth="1" min="98" max="98"/>
+    <col width="32.4" customWidth="1" min="99" max="99"/>
+    <col width="22.8" customWidth="1" min="100" max="100"/>
+    <col width="31.2" customWidth="1" min="101" max="101"/>
+    <col width="34.8" customWidth="1" min="102" max="102"/>
+    <col width="19.2" customWidth="1" min="103" max="103"/>
+    <col width="18" customWidth="1" min="104" max="104"/>
+    <col width="42" customWidth="1" min="105" max="105"/>
+    <col width="28.8" customWidth="1" min="106" max="106"/>
+    <col width="7.199999999999999" customWidth="1" min="107" max="107"/>
+    <col width="21.6" customWidth="1" min="108" max="108"/>
+    <col width="39.6" customWidth="1" min="109" max="109"/>
+    <col width="34.8" customWidth="1" min="110" max="110"/>
+    <col width="19.2" customWidth="1" min="111" max="111"/>
+    <col width="22.8" customWidth="1" min="112" max="112"/>
+    <col width="30" customWidth="1" min="113" max="113"/>
+    <col width="39.6" customWidth="1" min="114" max="114"/>
+    <col width="20.4" customWidth="1" min="115" max="115"/>
+    <col width="19.2" customWidth="1" min="116" max="116"/>
+    <col width="50" customWidth="1" min="117" max="117"/>
+    <col width="15.6" customWidth="1" min="118" max="118"/>
+    <col width="32.4" customWidth="1" min="119" max="119"/>
+    <col width="19.2" customWidth="1" min="120" max="120"/>
+    <col width="42" customWidth="1" min="121" max="121"/>
+    <col width="43.2" customWidth="1" min="122" max="122"/>
+    <col width="30" customWidth="1" min="123" max="123"/>
+    <col width="33.6" customWidth="1" min="124" max="124"/>
+    <col width="48" customWidth="1" min="125" max="125"/>
+    <col width="43.2" customWidth="1" min="126" max="126"/>
+    <col width="44.4" customWidth="1" min="127" max="127"/>
+    <col width="33.6" customWidth="1" min="128" max="128"/>
+    <col width="27.6" customWidth="1" min="129" max="129"/>
+    <col width="37.2" customWidth="1" min="130" max="130"/>
+    <col width="33.6" customWidth="1" min="131" max="131"/>
+    <col width="27.6" customWidth="1" min="132" max="132"/>
+    <col width="43.2" customWidth="1" min="133" max="133"/>
+    <col width="37.2" customWidth="1" min="134" max="134"/>
+    <col width="39.6" customWidth="1" min="135" max="135"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>← Back to CustExp Config</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>OIS010: CUSTOMER ORDER TYPES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>OOTYPE: Customer order - order types</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Customer order type</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Customer order category</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Next manual function</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>Authorization group</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>Business chain check</t>
+        </is>
+      </c>
+      <c r="H5" s="27" t="inlineStr">
+        <is>
+          <t>Panel sequence</t>
+        </is>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
+        <is>
+          <t>Customer order series</t>
+        </is>
+      </c>
+      <c r="J5" s="27" t="inlineStr">
+        <is>
+          <t>Entry option</t>
+        </is>
+      </c>
+      <c r="K5" s="27" t="inlineStr">
+        <is>
+          <t>Several warehouses permitted</t>
+        </is>
+      </c>
+      <c r="L5" s="27" t="inlineStr">
+        <is>
+          <t>Quantity sign</t>
+        </is>
+      </c>
+      <c r="M5" s="27" t="inlineStr">
+        <is>
+          <t>Sales price rule</t>
+        </is>
+      </c>
+      <c r="N5" s="27" t="inlineStr">
+        <is>
+          <t>Cost price rule</t>
+        </is>
+      </c>
+      <c r="O5" s="27" t="inlineStr">
+        <is>
+          <t>Availability check</t>
+        </is>
+      </c>
+      <c r="P5" s="27" t="inlineStr">
+        <is>
+          <t>Promotion check</t>
+        </is>
+      </c>
+      <c r="Q5" s="27" t="inlineStr">
+        <is>
+          <t>Inventory accounting code - order type</t>
+        </is>
+      </c>
+      <c r="R5" s="27" t="inlineStr">
+        <is>
+          <t>Check sequence - item ID</t>
+        </is>
+      </c>
+      <c r="S5" s="27" t="inlineStr">
+        <is>
+          <t>Line number interval</t>
+        </is>
+      </c>
+      <c r="T5" s="27" t="inlineStr">
+        <is>
+          <t>Minimum processing time</t>
+        </is>
+      </c>
+      <c r="U5" s="27" t="inlineStr">
+        <is>
+          <t>Allocation method</t>
+        </is>
+      </c>
+      <c r="V5" s="27" t="inlineStr">
+        <is>
+          <t>Sales support integration</t>
+        </is>
+      </c>
+      <c r="W5" s="27" t="inlineStr">
+        <is>
+          <t>Cost pricing at delivery</t>
+        </is>
+      </c>
+      <c r="X5" s="27" t="inlineStr">
+        <is>
+          <t>Pricing and discount setting</t>
+        </is>
+      </c>
+      <c r="Y5" s="27" t="inlineStr">
+        <is>
+          <t>Invoice series</t>
+        </is>
+      </c>
+      <c r="Z5" s="27" t="inlineStr">
+        <is>
+          <t>Advance invoicing</t>
+        </is>
+      </c>
+      <c r="AA5" s="27" t="inlineStr">
+        <is>
+          <t>Advance invoice series</t>
+        </is>
+      </c>
+      <c r="AB5" s="27" t="inlineStr">
+        <is>
+          <t>Summary invoice</t>
+        </is>
+      </c>
+      <c r="AC5" s="27" t="inlineStr">
+        <is>
+          <t>Update order received statistics</t>
+        </is>
+      </c>
+      <c r="AD5" s="27" t="inlineStr">
+        <is>
+          <t>Update sales statistics</t>
+        </is>
+      </c>
+      <c r="AE5" s="27" t="inlineStr">
+        <is>
+          <t>Print fixed customer text</t>
+        </is>
+      </c>
+      <c r="AF5" s="27" t="inlineStr">
+        <is>
+          <t>Print fixed item text</t>
+        </is>
+      </c>
+      <c r="AG5" s="27" t="inlineStr">
+        <is>
+          <t>Print fixed document text</t>
+        </is>
+      </c>
+      <c r="AH5" s="27" t="inlineStr">
+        <is>
+          <t>Default line type</t>
+        </is>
+      </c>
+      <c r="AI5" s="27" t="inlineStr">
+        <is>
+          <t>Abnormal demand</t>
+        </is>
+      </c>
+      <c r="AJ5" s="27" t="inlineStr">
+        <is>
+          <t>Bonus generating</t>
+        </is>
+      </c>
+      <c r="AK5" s="27" t="inlineStr">
+        <is>
+          <t>Commission generating</t>
+        </is>
+      </c>
+      <c r="AL5" s="27" t="inlineStr">
+        <is>
+          <t>Preliminary customer order</t>
+        </is>
+      </c>
+      <c r="AM5" s="27" t="inlineStr">
+        <is>
+          <t>Status - delivery order</t>
+        </is>
+      </c>
+      <c r="AN5" s="27" t="inlineStr">
+        <is>
+          <t>Reasonability check</t>
+        </is>
+      </c>
+      <c r="AO5" s="27" t="inlineStr">
+        <is>
+          <t>Contribution margin ratio check</t>
+        </is>
+      </c>
+      <c r="AP5" s="27" t="inlineStr">
+        <is>
+          <t>Statistics - lost sales</t>
+        </is>
+      </c>
+      <c r="AQ5" s="27" t="inlineStr">
+        <is>
+          <t>Check duplicates</t>
+        </is>
+      </c>
+      <c r="AR5" s="27" t="inlineStr">
+        <is>
+          <t>Check order charges</t>
+        </is>
+      </c>
+      <c r="AS5" s="27" t="inlineStr">
+        <is>
+          <t>Check item charges</t>
+        </is>
+      </c>
+      <c r="AT5" s="27" t="inlineStr">
+        <is>
+          <t>Shortage panel</t>
+        </is>
+      </c>
+      <c r="AU5" s="27" t="inlineStr">
+        <is>
+          <t>Update buying pattern</t>
+        </is>
+      </c>
+      <c r="AV5" s="27" t="inlineStr">
+        <is>
+          <t>Customer order entry messages</t>
+        </is>
+      </c>
+      <c r="AW5" s="27" t="inlineStr">
+        <is>
+          <t>Propose quantity</t>
+        </is>
+      </c>
+      <c r="AX5" s="27" t="inlineStr">
+        <is>
+          <t>Search sequence - alias type</t>
+        </is>
+      </c>
+      <c r="AY5" s="27" t="inlineStr">
+        <is>
+          <t>Total price permitted</t>
+        </is>
+      </c>
+      <c r="AZ5" s="27" t="inlineStr">
+        <is>
+          <t>Self invoicing</t>
+        </is>
+      </c>
+      <c r="BA5" s="27" t="inlineStr">
+        <is>
+          <t>Propose warehouse</t>
+        </is>
+      </c>
+      <c r="BB5" s="27" t="inlineStr">
+        <is>
+          <t>Supply model</t>
+        </is>
+      </c>
+      <c r="BC5" s="27" t="inlineStr">
+        <is>
+          <t>Automatic acquisition</t>
+        </is>
+      </c>
+      <c r="BD5" s="27" t="inlineStr">
+        <is>
+          <t>Automatic release</t>
+        </is>
+      </c>
+      <c r="BE5" s="27" t="inlineStr">
+        <is>
+          <t>Tolerance days early delivery</t>
+        </is>
+      </c>
+      <c r="BF5" s="27" t="inlineStr">
+        <is>
+          <t>Tolerance days late delivery</t>
+        </is>
+      </c>
+      <c r="BG5" s="27" t="inlineStr">
+        <is>
+          <t>External prices</t>
+        </is>
+      </c>
+      <c r="BH5" s="27" t="inlineStr">
+        <is>
+          <t>Check demand time fence</t>
+        </is>
+      </c>
+      <c r="BI5" s="27" t="inlineStr">
+        <is>
+          <t>Accepted deviation</t>
+        </is>
+      </c>
+      <c r="BJ5" s="27" t="inlineStr">
+        <is>
+          <t>Quantity fulfillment check method</t>
+        </is>
+      </c>
+      <c r="BK5" s="27" t="inlineStr">
+        <is>
+          <t>Credit check - new entry of order</t>
+        </is>
+      </c>
+      <c r="BL5" s="27" t="inlineStr">
+        <is>
+          <t>Credit check - new entry of lines</t>
+        </is>
+      </c>
+      <c r="BM5" s="27" t="inlineStr">
+        <is>
+          <t>Credit check - close</t>
+        </is>
+      </c>
+      <c r="BN5" s="27" t="inlineStr">
+        <is>
+          <t>Invoicing group</t>
+        </is>
+      </c>
+      <c r="BO5" s="27" t="inlineStr">
+        <is>
+          <t>Total line</t>
+        </is>
+      </c>
+      <c r="BP5" s="27" t="inlineStr">
+        <is>
+          <t>Update subfile</t>
+        </is>
+      </c>
+      <c r="BQ5" s="27" t="inlineStr">
+        <is>
+          <t>Sorting order - panel H</t>
+        </is>
+      </c>
+      <c r="BR5" s="27" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="BS5" s="27" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="BT5" s="27" t="inlineStr">
+        <is>
+          <t>Update cumulative weight</t>
+        </is>
+      </c>
+      <c r="BU5" s="27" t="inlineStr">
+        <is>
+          <t>Rounding-off category</t>
+        </is>
+      </c>
+      <c r="BV5" s="27" t="inlineStr">
+        <is>
+          <t>Auto level - invoicing</t>
+        </is>
+      </c>
+      <c r="BW5" s="27" t="inlineStr">
+        <is>
+          <t>Opening panel</t>
+        </is>
+      </c>
+      <c r="BX5" s="27" t="inlineStr">
+        <is>
+          <t>Agreement check</t>
+        </is>
+      </c>
+      <c r="BY5" s="27" t="inlineStr">
+        <is>
+          <t>Check planned split</t>
+        </is>
+      </c>
+      <c r="BZ5" s="27" t="inlineStr">
+        <is>
+          <t>Demand factor</t>
+        </is>
+      </c>
+      <c r="CA5" s="27" t="inlineStr">
+        <is>
+          <t>Round to packaging size</t>
+        </is>
+      </c>
+      <c r="CB5" s="27" t="inlineStr">
+        <is>
+          <t>Dispatch policy</t>
+        </is>
+      </c>
+      <c r="CC5" s="27" t="inlineStr">
+        <is>
+          <t>Season in use</t>
+        </is>
+      </c>
+      <c r="CD5" s="27" t="inlineStr">
+        <is>
+          <t>Costing model - sales price</t>
+        </is>
+      </c>
+      <c r="CE5" s="27" t="inlineStr">
+        <is>
+          <t>Price origin sequence</t>
+        </is>
+      </c>
+      <c r="CF5" s="27" t="inlineStr">
+        <is>
+          <t>Reschedule from when preall was changed</t>
+        </is>
+      </c>
+      <c r="CG5" s="27" t="inlineStr">
+        <is>
+          <t>Update preallocation when qty is changed</t>
+        </is>
+      </c>
+      <c r="CH5" s="27" t="inlineStr">
+        <is>
+          <t>Quotation date check</t>
+        </is>
+      </c>
+      <c r="CI5" s="27" t="inlineStr">
+        <is>
+          <t>Create quotas for customers with sts 10</t>
+        </is>
+      </c>
+      <c r="CJ5" s="27" t="inlineStr">
+        <is>
+          <t>Ignore payer block code</t>
+        </is>
+      </c>
+      <c r="CK5" s="27" t="inlineStr">
+        <is>
+          <t>Display delivery addresses</t>
+        </is>
+      </c>
+      <c r="CL5" s="27" t="inlineStr">
+        <is>
+          <t>Update delivered/not invoiced statistics</t>
+        </is>
+      </c>
+      <c r="CM5" s="27" t="inlineStr">
+        <is>
+          <t>Packaging action</t>
+        </is>
+      </c>
+      <c r="CN5" s="27" t="inlineStr">
+        <is>
+          <t>Quantity limit</t>
+        </is>
+      </c>
+      <c r="CO5" s="27" t="inlineStr">
+        <is>
+          <t>Price date check</t>
+        </is>
+      </c>
+      <c r="CP5" s="27" t="inlineStr">
+        <is>
+          <t>Best price</t>
+        </is>
+      </c>
+      <c r="CQ5" s="27" t="inlineStr">
+        <is>
+          <t>Automatic option</t>
+        </is>
+      </c>
+      <c r="CR5" s="27" t="inlineStr">
+        <is>
+          <t>Validate S/N</t>
+        </is>
+      </c>
+      <c r="CS5" s="27" t="inlineStr">
+        <is>
+          <t>Type of invoice</t>
+        </is>
+      </c>
+      <c r="CT5" s="27" t="inlineStr">
+        <is>
+          <t>Corrective invoice series</t>
+        </is>
+      </c>
+      <c r="CU5" s="27" t="inlineStr">
+        <is>
+          <t>Tax code customer/address</t>
+        </is>
+      </c>
+      <c r="CV5" s="27" t="inlineStr">
+        <is>
+          <t>Automatic closing</t>
+        </is>
+      </c>
+      <c r="CW5" s="27" t="inlineStr">
+        <is>
+          <t>Round promotion quantity</t>
+        </is>
+      </c>
+      <c r="CX5" s="27" t="inlineStr">
+        <is>
+          <t>Input alternative - panel B</t>
+        </is>
+      </c>
+      <c r="CY5" s="27" t="inlineStr">
+        <is>
+          <t>Action reasons</t>
+        </is>
+      </c>
+      <c r="CZ5" s="27" t="inlineStr">
+        <is>
+          <t>Initial order</t>
+        </is>
+      </c>
+      <c r="DA5" s="27" t="inlineStr">
+        <is>
+          <t>VAT calculation at goods delivery</t>
+        </is>
+      </c>
+      <c r="DB5" s="27" t="inlineStr">
+        <is>
+          <t>Payment request series</t>
+        </is>
+      </c>
+      <c r="DC5" s="27" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="DD5" s="27" t="inlineStr">
+        <is>
+          <t>Cash desk active</t>
+        </is>
+      </c>
+      <c r="DE5" s="27" t="inlineStr">
+        <is>
+          <t>Update order value without risk</t>
+        </is>
+      </c>
+      <c r="DF5" s="27" t="inlineStr">
+        <is>
+          <t>Several pieces of equipment</t>
+        </is>
+      </c>
+      <c r="DG5" s="27" t="inlineStr">
+        <is>
+          <t>Create address</t>
+        </is>
+      </c>
+      <c r="DH5" s="27" t="inlineStr">
+        <is>
+          <t>Item status check</t>
+        </is>
+      </c>
+      <c r="DI5" s="27" t="inlineStr">
+        <is>
+          <t>Payment document series</t>
+        </is>
+      </c>
+      <c r="DJ5" s="27" t="inlineStr">
+        <is>
+          <t>Supplier rebate agreement check</t>
+        </is>
+      </c>
+      <c r="DK5" s="27" t="inlineStr">
+        <is>
+          <t>Eco-calculation</t>
+        </is>
+      </c>
+      <c r="DL5" s="27" t="inlineStr">
+        <is>
+          <t>Price guidance</t>
+        </is>
+      </c>
+      <c r="DM5" s="27" t="inlineStr">
+        <is>
+          <t>Price origins blocked for price guidance</t>
+        </is>
+      </c>
+      <c r="DN5" s="27" t="inlineStr">
+        <is>
+          <t>Mixed order</t>
+        </is>
+      </c>
+      <c r="DO5" s="27" t="inlineStr">
+        <is>
+          <t>Prohibit negative charges</t>
+        </is>
+      </c>
+      <c r="DP5" s="27" t="inlineStr">
+        <is>
+          <t>Internal sales</t>
+        </is>
+      </c>
+      <c r="DQ5" s="27" t="inlineStr">
+        <is>
+          <t>Lost sales - endmark picking list</t>
+        </is>
+      </c>
+      <c r="DR5" s="27" t="inlineStr">
+        <is>
+          <t>Reason code - endmark picking list</t>
+        </is>
+      </c>
+      <c r="DS5" s="27" t="inlineStr">
+        <is>
+          <t>Lost sales - auto close</t>
+        </is>
+      </c>
+      <c r="DT5" s="27" t="inlineStr">
+        <is>
+          <t>Reason code - auto closing</t>
+        </is>
+      </c>
+      <c r="DU5" s="27" t="inlineStr">
+        <is>
+          <t>Quantity reason code - endmark picking</t>
+        </is>
+      </c>
+      <c r="DV5" s="27" t="inlineStr">
+        <is>
+          <t>Reason code - endmark picking list</t>
+        </is>
+      </c>
+      <c r="DW5" s="27" t="inlineStr">
+        <is>
+          <t>Quantity reason code - auto closing</t>
+        </is>
+      </c>
+      <c r="DX5" s="27" t="inlineStr">
+        <is>
+          <t>Reason code - auto closing</t>
+        </is>
+      </c>
+      <c r="DY5" s="27" t="inlineStr">
+        <is>
+          <t>Not for debit invoice</t>
+        </is>
+      </c>
+      <c r="DZ5" s="27" t="inlineStr">
+        <is>
+          <t>Price/disc recalculation rule</t>
+        </is>
+      </c>
+      <c r="EA5" s="27" t="inlineStr">
+        <is>
+          <t>Customer order type status</t>
+        </is>
+      </c>
+      <c r="EB5" s="27" t="inlineStr">
+        <is>
+          <t>Deposit payment terms</t>
+        </is>
+      </c>
+      <c r="EC5" s="27" t="inlineStr">
+        <is>
+          <t>Allow manual entry of order number</t>
+        </is>
+      </c>
+      <c r="ED5" s="27" t="inlineStr">
+        <is>
+          <t>Credit advance invoice series</t>
+        </is>
+      </c>
+      <c r="EE5" s="27" t="inlineStr">
+        <is>
+          <t>Deposit for stocked order lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>ORTP</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>ORTK</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>TX40</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>TX15</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>AUGP</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>OT01</t>
+        </is>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>OT04</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>OT05</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>OT06</t>
+        </is>
+      </c>
+      <c r="K6" s="28" t="inlineStr">
+        <is>
+          <t>OT10</t>
+        </is>
+      </c>
+      <c r="L6" s="28" t="inlineStr">
+        <is>
+          <t>OT11</t>
+        </is>
+      </c>
+      <c r="M6" s="28" t="inlineStr">
+        <is>
+          <t>OT12</t>
+        </is>
+      </c>
+      <c r="N6" s="28" t="inlineStr">
+        <is>
+          <t>OT14</t>
+        </is>
+      </c>
+      <c r="O6" s="28" t="inlineStr">
+        <is>
+          <t>OT15</t>
+        </is>
+      </c>
+      <c r="P6" s="28" t="inlineStr">
+        <is>
+          <t>OT17</t>
+        </is>
+      </c>
+      <c r="Q6" s="28" t="inlineStr">
+        <is>
+          <t>OT18</t>
+        </is>
+      </c>
+      <c r="R6" s="28" t="inlineStr">
+        <is>
+          <t>OT19</t>
+        </is>
+      </c>
+      <c r="S6" s="28" t="inlineStr">
+        <is>
+          <t>OT20</t>
+        </is>
+      </c>
+      <c r="T6" s="28" t="inlineStr">
+        <is>
+          <t>OT22</t>
+        </is>
+      </c>
+      <c r="U6" s="28" t="inlineStr">
+        <is>
+          <t>OT25</t>
+        </is>
+      </c>
+      <c r="V6" s="28" t="inlineStr">
+        <is>
+          <t>OT26</t>
+        </is>
+      </c>
+      <c r="W6" s="28" t="inlineStr">
+        <is>
+          <t>OT30</t>
+        </is>
+      </c>
+      <c r="X6" s="28" t="inlineStr">
+        <is>
+          <t>OT31</t>
+        </is>
+      </c>
+      <c r="Y6" s="28" t="inlineStr">
+        <is>
+          <t>OT34</t>
+        </is>
+      </c>
+      <c r="Z6" s="28" t="inlineStr">
+        <is>
+          <t>OT35</t>
+        </is>
+      </c>
+      <c r="AA6" s="28" t="inlineStr">
+        <is>
+          <t>OT36</t>
+        </is>
+      </c>
+      <c r="AB6" s="28" t="inlineStr">
+        <is>
+          <t>OT37</t>
+        </is>
+      </c>
+      <c r="AC6" s="28" t="inlineStr">
+        <is>
+          <t>OT38</t>
+        </is>
+      </c>
+      <c r="AD6" s="28" t="inlineStr">
+        <is>
+          <t>OT39</t>
+        </is>
+      </c>
+      <c r="AE6" s="28" t="inlineStr">
+        <is>
+          <t>OT42</t>
+        </is>
+      </c>
+      <c r="AF6" s="28" t="inlineStr">
+        <is>
+          <t>OT45</t>
+        </is>
+      </c>
+      <c r="AG6" s="28" t="inlineStr">
+        <is>
+          <t>OT46</t>
+        </is>
+      </c>
+      <c r="AH6" s="28" t="inlineStr">
+        <is>
+          <t>OT47</t>
+        </is>
+      </c>
+      <c r="AI6" s="28" t="inlineStr">
+        <is>
+          <t>OT53</t>
+        </is>
+      </c>
+      <c r="AJ6" s="28" t="inlineStr">
+        <is>
+          <t>OT54</t>
+        </is>
+      </c>
+      <c r="AK6" s="28" t="inlineStr">
+        <is>
+          <t>OT55</t>
+        </is>
+      </c>
+      <c r="AL6" s="28" t="inlineStr">
+        <is>
+          <t>OT59</t>
+        </is>
+      </c>
+      <c r="AM6" s="28" t="inlineStr">
+        <is>
+          <t>OT60</t>
+        </is>
+      </c>
+      <c r="AN6" s="28" t="inlineStr">
+        <is>
+          <t>OT61</t>
+        </is>
+      </c>
+      <c r="AO6" s="28" t="inlineStr">
+        <is>
+          <t>OT63</t>
+        </is>
+      </c>
+      <c r="AP6" s="28" t="inlineStr">
+        <is>
+          <t>OT65</t>
+        </is>
+      </c>
+      <c r="AQ6" s="28" t="inlineStr">
+        <is>
+          <t>OT66</t>
+        </is>
+      </c>
+      <c r="AR6" s="28" t="inlineStr">
+        <is>
+          <t>OT67</t>
+        </is>
+      </c>
+      <c r="AS6" s="28" t="inlineStr">
+        <is>
+          <t>OT68</t>
+        </is>
+      </c>
+      <c r="AT6" s="28" t="inlineStr">
+        <is>
+          <t>OT69</t>
+        </is>
+      </c>
+      <c r="AU6" s="28" t="inlineStr">
+        <is>
+          <t>OT70</t>
+        </is>
+      </c>
+      <c r="AV6" s="28" t="inlineStr">
+        <is>
+          <t>OT71</t>
+        </is>
+      </c>
+      <c r="AW6" s="28" t="inlineStr">
+        <is>
+          <t>OT72</t>
+        </is>
+      </c>
+      <c r="AX6" s="28" t="inlineStr">
+        <is>
+          <t>OT73</t>
+        </is>
+      </c>
+      <c r="AY6" s="28" t="inlineStr">
+        <is>
+          <t>OT74</t>
+        </is>
+      </c>
+      <c r="AZ6" s="28" t="inlineStr">
+        <is>
+          <t>OT75</t>
+        </is>
+      </c>
+      <c r="BA6" s="28" t="inlineStr">
+        <is>
+          <t>OT77</t>
+        </is>
+      </c>
+      <c r="BB6" s="28" t="inlineStr">
+        <is>
+          <t>SPLM</t>
+        </is>
+      </c>
+      <c r="BC6" s="28" t="inlineStr">
+        <is>
+          <t>OT80</t>
+        </is>
+      </c>
+      <c r="BD6" s="28" t="inlineStr">
+        <is>
+          <t>OT81</t>
+        </is>
+      </c>
+      <c r="BE6" s="28" t="inlineStr">
+        <is>
+          <t>OT84</t>
+        </is>
+      </c>
+      <c r="BF6" s="28" t="inlineStr">
+        <is>
+          <t>OT85</t>
+        </is>
+      </c>
+      <c r="BG6" s="28" t="inlineStr">
+        <is>
+          <t>OT86</t>
+        </is>
+      </c>
+      <c r="BH6" s="28" t="inlineStr">
+        <is>
+          <t>OT88</t>
+        </is>
+      </c>
+      <c r="BI6" s="28" t="inlineStr">
+        <is>
+          <t>PDAD</t>
+        </is>
+      </c>
+      <c r="BJ6" s="28" t="inlineStr">
+        <is>
+          <t>QFCT</t>
+        </is>
+      </c>
+      <c r="BK6" s="28" t="inlineStr">
+        <is>
+          <t>CLOE</t>
+        </is>
+      </c>
+      <c r="BL6" s="28" t="inlineStr">
+        <is>
+          <t>CLLE</t>
+        </is>
+      </c>
+      <c r="BM6" s="28" t="inlineStr">
+        <is>
+          <t>CLOQ</t>
+        </is>
+      </c>
+      <c r="BN6" s="28" t="inlineStr">
+        <is>
+          <t>IVGP</t>
+        </is>
+      </c>
+      <c r="BO6" s="28" t="inlineStr">
+        <is>
+          <t>TOLI</t>
+        </is>
+      </c>
+      <c r="BP6" s="28" t="inlineStr">
+        <is>
+          <t>SFUP</t>
+        </is>
+      </c>
+      <c r="BQ6" s="28" t="inlineStr">
+        <is>
+          <t>QTTH</t>
+        </is>
+      </c>
+      <c r="BR6" s="28" t="inlineStr">
+        <is>
+          <t>PAVR</t>
+        </is>
+      </c>
+      <c r="BS6" s="28" t="inlineStr">
+        <is>
+          <t>PAV2</t>
+        </is>
+      </c>
+      <c r="BT6" s="28" t="inlineStr">
+        <is>
+          <t>AGWU</t>
+        </is>
+      </c>
+      <c r="BU6" s="28" t="inlineStr">
+        <is>
+          <t>ROPP</t>
+        </is>
+      </c>
+      <c r="BV6" s="28" t="inlineStr">
+        <is>
+          <t>IVLV</t>
+        </is>
+      </c>
+      <c r="BW6" s="28" t="inlineStr">
+        <is>
+          <t>SPIC</t>
+        </is>
+      </c>
+      <c r="BX6" s="28" t="inlineStr">
+        <is>
+          <t>AGCL</t>
+        </is>
+      </c>
+      <c r="BY6" s="28" t="inlineStr">
+        <is>
+          <t>OT89</t>
+        </is>
+      </c>
+      <c r="BZ6" s="28" t="inlineStr">
+        <is>
+          <t>DEFC</t>
+        </is>
+      </c>
+      <c r="CA6" s="28" t="inlineStr">
+        <is>
+          <t>ROPK</t>
+        </is>
+      </c>
+      <c r="CB6" s="28" t="inlineStr">
+        <is>
+          <t>DPOL</t>
+        </is>
+      </c>
+      <c r="CC6" s="28" t="inlineStr">
+        <is>
+          <t>SEAH</t>
+        </is>
+      </c>
+      <c r="CD6" s="28" t="inlineStr">
+        <is>
+          <t>SCMO</t>
+        </is>
+      </c>
+      <c r="CE6" s="28" t="inlineStr">
+        <is>
+          <t>PRMS</t>
+        </is>
+      </c>
+      <c r="CF6" s="28" t="inlineStr">
+        <is>
+          <t>PTRG</t>
+        </is>
+      </c>
+      <c r="CG6" s="28" t="inlineStr">
+        <is>
+          <t>PTQC</t>
+        </is>
+      </c>
+      <c r="CH6" s="28" t="inlineStr">
+        <is>
+          <t>QDCK</t>
+        </is>
+      </c>
+      <c r="CI6" s="28" t="inlineStr">
+        <is>
+          <t>QSCK</t>
+        </is>
+      </c>
+      <c r="CJ6" s="28" t="inlineStr">
+        <is>
+          <t>AUBC</t>
+        </is>
+      </c>
+      <c r="CK6" s="28" t="inlineStr">
+        <is>
+          <t>DELA</t>
+        </is>
+      </c>
+      <c r="CL6" s="28" t="inlineStr">
+        <is>
+          <t>UPDE</t>
+        </is>
+      </c>
+      <c r="CM6" s="28" t="inlineStr">
+        <is>
+          <t>PCKA</t>
+        </is>
+      </c>
+      <c r="CN6" s="28" t="inlineStr">
+        <is>
+          <t>QLCH</t>
+        </is>
+      </c>
+      <c r="CO6" s="28" t="inlineStr">
+        <is>
+          <t>PDCH</t>
+        </is>
+      </c>
+      <c r="CP6" s="28" t="inlineStr">
+        <is>
+          <t>BEPR</t>
+        </is>
+      </c>
+      <c r="CQ6" s="28" t="inlineStr">
+        <is>
+          <t>AOPT</t>
+        </is>
+      </c>
+      <c r="CR6" s="28" t="inlineStr">
+        <is>
+          <t>OT91</t>
+        </is>
+      </c>
+      <c r="CS6" s="28" t="inlineStr">
+        <is>
+          <t>XTPI</t>
+        </is>
+      </c>
+      <c r="CT6" s="28" t="inlineStr">
+        <is>
+          <t>OT79</t>
+        </is>
+      </c>
+      <c r="CU6" s="28" t="inlineStr">
+        <is>
+          <t>TAXC</t>
+        </is>
+      </c>
+      <c r="CV6" s="28" t="inlineStr">
+        <is>
+          <t>BOP1</t>
+        </is>
+      </c>
+      <c r="CW6" s="28" t="inlineStr">
+        <is>
+          <t>RPRQ</t>
+        </is>
+      </c>
+      <c r="CX6" s="28" t="inlineStr">
+        <is>
+          <t>QTTB</t>
+        </is>
+      </c>
+      <c r="CY6" s="28" t="inlineStr">
+        <is>
+          <t>ARES</t>
+        </is>
+      </c>
+      <c r="CZ6" s="28" t="inlineStr">
+        <is>
+          <t>INOR</t>
+        </is>
+      </c>
+      <c r="DA6" s="28" t="inlineStr">
+        <is>
+          <t>VTDE</t>
+        </is>
+      </c>
+      <c r="DB6" s="28" t="inlineStr">
+        <is>
+          <t>PRSE</t>
+        </is>
+      </c>
+      <c r="DC6" s="28" t="inlineStr">
+        <is>
+          <t>PAV4</t>
+        </is>
+      </c>
+      <c r="DD6" s="28" t="inlineStr">
+        <is>
+          <t>CAPM</t>
+        </is>
+      </c>
+      <c r="DE6" s="28" t="inlineStr">
+        <is>
+          <t>UOVW</t>
+        </is>
+      </c>
+      <c r="DF6" s="28" t="inlineStr">
+        <is>
+          <t>OT92</t>
+        </is>
+      </c>
+      <c r="DG6" s="28" t="inlineStr">
+        <is>
+          <t>CRAD</t>
+        </is>
+      </c>
+      <c r="DH6" s="28" t="inlineStr">
+        <is>
+          <t>ITSC</t>
+        </is>
+      </c>
+      <c r="DI6" s="28" t="inlineStr">
+        <is>
+          <t>OT83</t>
+        </is>
+      </c>
+      <c r="DJ6" s="28" t="inlineStr">
+        <is>
+          <t>RACH</t>
+        </is>
+      </c>
+      <c r="DK6" s="28" t="inlineStr">
+        <is>
+          <t>OTA6</t>
+        </is>
+      </c>
+      <c r="DL6" s="28" t="inlineStr">
+        <is>
+          <t>PRGU</t>
+        </is>
+      </c>
+      <c r="DM6" s="28" t="inlineStr">
+        <is>
+          <t>OBPG</t>
+        </is>
+      </c>
+      <c r="DN6" s="28" t="inlineStr">
+        <is>
+          <t>MIXO</t>
+        </is>
+      </c>
+      <c r="DO6" s="28" t="inlineStr">
+        <is>
+          <t>DANC</t>
+        </is>
+      </c>
+      <c r="DP6" s="28" t="inlineStr">
+        <is>
+          <t>ICTR</t>
+        </is>
+      </c>
+      <c r="DQ6" s="28" t="inlineStr">
+        <is>
+          <t>LS03</t>
+        </is>
+      </c>
+      <c r="DR6" s="28" t="inlineStr">
+        <is>
+          <t>RS03</t>
+        </is>
+      </c>
+      <c r="DS6" s="28" t="inlineStr">
+        <is>
+          <t>LS04</t>
+        </is>
+      </c>
+      <c r="DT6" s="28" t="inlineStr">
+        <is>
+          <t>RS04</t>
+        </is>
+      </c>
+      <c r="DU6" s="28" t="inlineStr">
+        <is>
+          <t>QR15</t>
+        </is>
+      </c>
+      <c r="DV6" s="28" t="inlineStr">
+        <is>
+          <t>RS15</t>
+        </is>
+      </c>
+      <c r="DW6" s="28" t="inlineStr">
+        <is>
+          <t>QR16</t>
+        </is>
+      </c>
+      <c r="DX6" s="28" t="inlineStr">
+        <is>
+          <t>RS16</t>
+        </is>
+      </c>
+      <c r="DY6" s="28" t="inlineStr">
+        <is>
+          <t>NFDI</t>
+        </is>
+      </c>
+      <c r="DZ6" s="28" t="inlineStr">
+        <is>
+          <t>RCRU</t>
+        </is>
+      </c>
+      <c r="EA6" s="28" t="inlineStr">
+        <is>
+          <t>CSTA</t>
+        </is>
+      </c>
+      <c r="EB6" s="28" t="inlineStr">
+        <is>
+          <t>DEPY</t>
+        </is>
+      </c>
+      <c r="EC6" s="28" t="inlineStr">
+        <is>
+          <t>BMON</t>
+        </is>
+      </c>
+      <c r="ED6" s="28" t="inlineStr">
+        <is>
+          <t>CAIS</t>
+        </is>
+      </c>
+      <c r="EE6" s="28" t="inlineStr">
+        <is>
+          <t>DSOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AC7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AD7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AE7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AG7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AH7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AI7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AJ7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AK7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AM7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AO7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AP7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AQ7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AR7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AS7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AT7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AU7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AV7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AW7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AX7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AY7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AZ7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BA7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BB7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BC7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BD7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BE7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BF7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BG7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BI7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BJ7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BK7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BL7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BM7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BN7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BO7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BP7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BQ7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BR7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BT7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BU7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BV7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BW7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BX7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BY7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BZ7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CA7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CB7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CC7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CD7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CE7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CF7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CG7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CH7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CI7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CJ7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CK7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CL7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CM7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CN7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CO7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CP7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CQ7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CR7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CS7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CT7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CU7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CV7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CW7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CX7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CY7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CZ7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DA7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DB7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DC7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DD7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DE7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DF7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DG7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DH7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DI7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DJ7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DK7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DL7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DM7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DN7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DO7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DP7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DQ7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DR7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DS7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DT7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DU7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DV7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DW7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DX7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DY7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DZ7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="EA7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EB7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EC7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="ED7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EE7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM8" s="30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AP8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AQ8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AR8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AT8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AU8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AX8" s="30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BB8" s="30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BC8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BF8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BG8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BI8" s="30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BL8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BM8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BO8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BQ8" s="30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BR8" s="30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BS8" s="30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BT8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU8" s="30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BV8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BW8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BX8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BY8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BZ8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="CA8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CB8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="CC8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CD8" s="30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CE8" s="30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="CF8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CG8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CH8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CI8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CJ8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CK8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CL8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CM8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CN8" s="30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CO8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="CP8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CQ8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CR8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CS8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CT8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CU8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="CV8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CW8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CX8" s="30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CY8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CZ8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DA8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DB8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DC8" s="30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="DD8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DE8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DF8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DG8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DH8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DI8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DJ8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DK8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DL8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DM8" s="30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="DN8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DO8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DP8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DQ8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DR8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="DS8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DT8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="DU8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DV8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="DW8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DX8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="DY8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="DZ8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="EA8" s="30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="EB8" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="EC8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="ED8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="EE8" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>